--- a/docs/downloads/经营分_津河省区__津北片区_2026-10-19.xlsx
+++ b/docs/downloads/经营分_津河省区__津北片区_2026-10-19.xlsx
@@ -12,7 +12,7 @@
     <sheet name="匹配异常" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'门店经营分'!$A$1:$V$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'门店经营分'!$A$1:$V$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'匹配异常'!$A$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V22"/>
+  <dimension ref="A1:V23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1020,24 +1020,20 @@
           <t>津北片区</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>天津市</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>7222162953171109903</t>
+          <t>6914401232568190990</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>丽怡酒店（天津武清开发区万达店）</t>
+          <t>维也纳3好酒店(天津淮河道地铁站店)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>丽怡酒店(天津武清开发区万达店)</t>
+          <t>维也纳3好酒店(天津淮河道地铁站店)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1046,10 +1042,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I6" t="n">
-        <v>-5</v>
+        <v>7</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1063,7 +1059,7 @@
         <v>10</v>
       </c>
       <c r="M6" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="N6" t="n">
         <v>30</v>
@@ -1075,7 +1071,7 @@
         <v>30</v>
       </c>
       <c r="Q6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="R6" t="n">
         <v>30</v>
@@ -1115,29 +1111,29 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>6960652153400592414</t>
+          <t>7222162953171109903</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>喆啡酒店（天津火车站天津之眼中山路地铁站店）</t>
+          <t>丽怡酒店（天津武清开发区万达店）</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>喆啡酒店(天津火车站天津之眼中山路地铁站店)</t>
+          <t>丽怡酒店(天津武清开发区万达店)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1163,7 +1159,7 @@
         <v>30</v>
       </c>
       <c r="Q7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R7" t="n">
         <v>30</v>
@@ -1203,29 +1199,29 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>6819941238427502596</t>
+          <t>6960652153400592414</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>维也纳智好酒店（天津之眼古文化街店）</t>
+          <t>喆啡酒店（天津火车站天津之眼中山路地铁站店）</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>维也纳智好酒店(天津之眼店)</t>
+          <t>喆啡酒店(天津火车站天津之眼中山路地铁站店)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H8" t="n">
         <v>87</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1239,19 +1235,19 @@
         <v>10</v>
       </c>
       <c r="M8" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="N8" t="n">
         <v>30</v>
       </c>
       <c r="O8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P8" t="n">
         <v>30</v>
       </c>
       <c r="Q8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="R8" t="n">
         <v>30</v>
@@ -1291,29 +1287,29 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>6601273342836082702</t>
+          <t>6819941238427502596</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>维也纳酒店（天津武清大华总部店）</t>
+          <t>维也纳智好酒店（天津之眼古文化街店）</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>维也纳酒店(天津武清大华总部店)</t>
+          <t>维也纳智好酒店(天津之眼店)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H9" t="n">
         <v>87</v>
       </c>
       <c r="I9" t="n">
-        <v>-5</v>
+        <v>7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1327,7 +1323,7 @@
         <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="N9" t="n">
         <v>30</v>
@@ -1339,7 +1335,7 @@
         <v>30</v>
       </c>
       <c r="Q9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="R9" t="n">
         <v>30</v>
@@ -1379,17 +1375,17 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>7081318591441668127</t>
+          <t>6601273342836082702</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>麗枫酒店· 天津站意式风情区天津之眼店</t>
+          <t>维也纳酒店（天津武清大华总部店）</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津火车站意大利风情街店)</t>
+          <t>维也纳酒店(天津武清大华总部店)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1401,7 +1397,7 @@
         <v>87</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1421,13 +1417,13 @@
         <v>30</v>
       </c>
       <c r="O10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P10" t="n">
         <v>30</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R10" t="n">
         <v>30</v>
@@ -1467,17 +1463,17 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>6601256643759966222</t>
+          <t>7081318591441668127</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>麗枫酒店·天津武清高铁站大光明中心店</t>
+          <t>麗枫酒店· 天津站意式风情区天津之眼店</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津武清高铁站大光明中心店)</t>
+          <t>麗枫酒店(天津火车站意大利风情街店)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1489,7 +1485,7 @@
         <v>87</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1555,17 +1551,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>7278641233155590185</t>
+          <t>6601256643759966222</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>维也纳智好天津北辰西堤头店</t>
+          <t>麗枫酒店·天津武清高铁站大光明中心店</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>维也纳酒店(天津北辰西堤头店)</t>
+          <t>麗枫酒店(天津武清高铁站大光明中心店)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1574,18 +1570,18 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I12" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L12" t="n">
         <v>10</v>
@@ -1603,7 +1599,7 @@
         <v>30</v>
       </c>
       <c r="Q12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R12" t="n">
         <v>30</v>
@@ -1643,37 +1639,37 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>6924421482093234189</t>
+          <t>7278641233155590185</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>希岸Deluxe酒店天津武清友谊百货店</t>
+          <t>维也纳智好天津北辰西堤头店</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>希岸Deluxe酒店(天津武清友谊百货店)</t>
+          <t>维也纳酒店(天津北辰西堤头店)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>搭门店,稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
         <v>10</v>
@@ -1685,13 +1681,13 @@
         <v>30</v>
       </c>
       <c r="O13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P13" t="n">
         <v>30</v>
       </c>
       <c r="Q13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R13" t="n">
         <v>30</v>
@@ -1731,17 +1727,17 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>7013563128763910175</t>
+          <t>6924421482093234189</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>麗枫酒店·天津北辰道儿童医院刘园地铁站店</t>
+          <t>希岸Deluxe酒店天津武清友谊百货店</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津北辰道儿童医院刘园地铁站店)</t>
+          <t>希岸Deluxe酒店(天津武清友谊百货店)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1753,7 +1749,7 @@
         <v>92</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1773,13 +1769,13 @@
         <v>30</v>
       </c>
       <c r="O14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P14" t="n">
         <v>30</v>
       </c>
       <c r="Q14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R14" t="n">
         <v>30</v>
@@ -1819,29 +1815,29 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>7428829464932386852</t>
+          <t>7013563128763910175</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>麗枫酒店（天津武清京清汽车产业园店）</t>
+          <t>麗枫酒店·天津北辰道儿童医院刘园地铁站店</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津武清京清汽车产业园店)</t>
+          <t>麗枫酒店(天津北辰道儿童医院刘园地铁站店)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H15" t="n">
         <v>92</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1861,13 +1857,13 @@
         <v>30</v>
       </c>
       <c r="O15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P15" t="n">
         <v>30</v>
       </c>
       <c r="Q15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R15" t="n">
         <v>30</v>
@@ -1907,17 +1903,17 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>6601137938665310216</t>
+          <t>7428829464932386852</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>锦江之星天津之眼中山路酒店</t>
+          <t>麗枫酒店（天津武清京清汽车产业园店）</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>锦江之星(天津中山路店)</t>
+          <t>麗枫酒店(天津武清京清汽车产业园店)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1926,7 +1922,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1943,19 +1939,19 @@
         <v>10</v>
       </c>
       <c r="M16" t="n">
+        <v>22</v>
+      </c>
+      <c r="N16" t="n">
+        <v>30</v>
+      </c>
+      <c r="O16" t="n">
         <v>25</v>
       </c>
-      <c r="N16" t="n">
-        <v>30</v>
-      </c>
-      <c r="O16" t="n">
-        <v>20</v>
-      </c>
       <c r="P16" t="n">
         <v>30</v>
       </c>
       <c r="Q16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R16" t="n">
         <v>30</v>
@@ -1995,17 +1991,17 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>6760527857455220743</t>
+          <t>6601137938665310216</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7天优品（天津古文化街天津之眼店）</t>
+          <t>锦江之星天津之眼中山路酒店</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>7天优品酒店(天津古文化街天津之眼店)</t>
+          <t>锦江之星(天津中山路店)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2014,7 +2010,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2043,7 +2039,7 @@
         <v>30</v>
       </c>
       <c r="Q17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R17" t="n">
         <v>30</v>
@@ -2083,22 +2079,22 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>6601139129520506893</t>
+          <t>6760527857455220743</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>喆啡酒店（天津火车站天津之眼店）</t>
+          <t>7天优品（天津古文化街天津之眼店）</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>喆啡酒店(天津火车站天津之眼店)</t>
+          <t>7天优品酒店(天津古文化街天津之眼店)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2109,7 +2105,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -2119,7 +2115,7 @@
         <v>10</v>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N18" t="n">
         <v>30</v>
@@ -2131,7 +2127,7 @@
         <v>30</v>
       </c>
       <c r="Q18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R18" t="n">
         <v>30</v>
@@ -2171,33 +2167,33 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>6684817408277891079</t>
+          <t>6601139129520506893</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>维也纳3好酒店（天津北辰双街柴楼地铁站店）</t>
+          <t>喆啡酒店（天津火车站天津之眼店）</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(天津北辰双街柴楼地铁站店)</t>
+          <t>喆啡酒店(天津火车站天津之眼店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -2207,13 +2203,13 @@
         <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N19" t="n">
         <v>30</v>
       </c>
       <c r="O19" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P19" t="n">
         <v>30</v>
@@ -2259,17 +2255,17 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>7232169595811924026</t>
+          <t>6684817408277891079</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>维也纳酒店（天津北辰区华北集团地铁站店）</t>
+          <t>维也纳3好酒店（天津北辰双街柴楼地铁站店）</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>维也纳酒店(天津北辰区华北集团地铁站店)</t>
+          <t>维也纳3好酒店(天津北辰双街柴楼地铁站店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2281,7 +2277,7 @@
         <v>105</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -2347,17 +2343,17 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>7487536797837166592</t>
+          <t>7232169595811924026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>7天优品酒店（天津北辰双街工业园区柴楼地铁站店）</t>
+          <t>维也纳酒店（天津北辰区华北集团地铁站店）</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>7天优品酒店(天津北辰柴楼地铁站店)</t>
+          <t>维也纳酒店(天津北辰区华北集团地铁站店)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2366,14 +2362,14 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="I21" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>稳房源</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -2395,7 +2391,7 @@
         <v>30</v>
       </c>
       <c r="Q21" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="R21" t="n">
         <v>30</v>
@@ -2435,79 +2431,167 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
+          <t>7487536797837166592</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>7天优品酒店（天津北辰双街工业园区柴楼地铁站店）</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>7天优品酒店(天津北辰柴楼地铁站店)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>已认证</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>115</v>
+      </c>
+      <c r="I22" t="n">
+        <v>18</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>稳房源</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>10</v>
+      </c>
+      <c r="L22" t="n">
+        <v>10</v>
+      </c>
+      <c r="M22" t="n">
+        <v>25</v>
+      </c>
+      <c r="N22" t="n">
+        <v>30</v>
+      </c>
+      <c r="O22" t="n">
+        <v>30</v>
+      </c>
+      <c r="P22" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>30</v>
+      </c>
+      <c r="R22" t="n">
+        <v>30</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="n">
+        <v>20</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>7249997748999555075</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>汇通百达网络科技（上海）有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>津河省区</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>津北片区</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
           <t>7140795379049580552</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>喆啡酒店天津西站天津之眼店</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>喆啡酒店(天津西站天津之眼店)</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>未认证</t>
         </is>
       </c>
-      <c r="H22" t="n">
+      <c r="H23" t="n">
         <v>120</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I23" t="n">
         <v>0</v>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="K22" t="n">
-        <v>10</v>
-      </c>
-      <c r="L22" t="n">
-        <v>10</v>
-      </c>
-      <c r="M22" t="n">
-        <v>30</v>
-      </c>
-      <c r="N22" t="n">
-        <v>30</v>
-      </c>
-      <c r="O22" t="n">
-        <v>30</v>
-      </c>
-      <c r="P22" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>30</v>
-      </c>
-      <c r="R22" t="n">
-        <v>30</v>
-      </c>
-      <c r="S22" t="n">
-        <v>20</v>
-      </c>
-      <c r="T22" t="n">
-        <v>20</v>
-      </c>
-      <c r="U22" t="inlineStr">
+      <c r="K23" t="n">
+        <v>10</v>
+      </c>
+      <c r="L23" t="n">
+        <v>10</v>
+      </c>
+      <c r="M23" t="n">
+        <v>30</v>
+      </c>
+      <c r="N23" t="n">
+        <v>30</v>
+      </c>
+      <c r="O23" t="n">
+        <v>30</v>
+      </c>
+      <c r="P23" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>30</v>
+      </c>
+      <c r="R23" t="n">
+        <v>30</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="n">
+        <v>20</v>
+      </c>
+      <c r="U23" t="inlineStr">
         <is>
           <t>7249997748999555075</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>汇通百达网络科技（上海）有限公司</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V22"/>
-  <conditionalFormatting sqref="H2:H22">
+  <autoFilter ref="A1:V23"/>
+  <conditionalFormatting sqref="H2:H23">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2519,7 +2603,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I22">
+  <conditionalFormatting sqref="I2:I23">
     <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
